--- a/List_Books.xlsx
+++ b/List_Books.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_F9185D456C1B742DE22F5EB5660250CE932DE984" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3ABF7705-0D6B-47C9-92AF-82CFA8F63A41}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68EB7091-8859-43F8-83CB-CF9955AC0EBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,9 +22,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="25">
   <si>
-    <t>Books Name</t>
-  </si>
-  <si>
     <t>Author</t>
   </si>
   <si>
@@ -95,12 +92,15 @@
   </si>
   <si>
     <t>Adam Fitri</t>
+  </si>
+  <si>
+    <t>Book Name</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <fonts count="4">
     <font>
       <sz val="11"/>
@@ -186,7 +186,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -194,20 +194,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Good" xfId="1" builtinId="26"/>
@@ -215,7 +214,9 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{2039F7F8-8406-4647-8D05-41446E418C4A}"/>
+  </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -498,30 +499,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="5:22" ht="15" customHeight="1">
-      <c r="E1" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
-      <c r="M1" s="7"/>
-      <c r="N1" s="7"/>
-      <c r="O1" s="7"/>
-      <c r="P1" s="7"/>
-      <c r="Q1" s="7"/>
-      <c r="R1" s="7"/>
-      <c r="S1" s="7"/>
-      <c r="T1" s="7"/>
-      <c r="U1" s="7"/>
-      <c r="V1" s="7"/>
+      <c r="E1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
+      <c r="N1" s="5"/>
+      <c r="O1" s="5"/>
+      <c r="P1" s="5"/>
+      <c r="Q1" s="5"/>
+      <c r="R1" s="5"/>
+      <c r="S1" s="5"/>
+      <c r="T1" s="5"/>
+      <c r="U1" s="5"/>
+      <c r="V1" s="5"/>
     </row>
     <row r="2" spans="5:22" ht="15" customHeight="1">
       <c r="E2" s="6" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F2" s="6"/>
       <c r="G2" s="6"/>
@@ -543,7 +544,7 @@
     </row>
     <row r="3" spans="5:22" ht="15" customHeight="1">
       <c r="E3" s="6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
@@ -565,221 +566,221 @@
     </row>
     <row r="5" spans="5:22">
       <c r="H5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="J5" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3"/>
+      <c r="M5" s="3"/>
+      <c r="O5" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="K5" s="4"/>
-      <c r="L5" s="4"/>
-      <c r="M5" s="4"/>
-      <c r="O5" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="P5" s="4"/>
-      <c r="Q5" s="4"/>
-      <c r="R5" s="4"/>
+      <c r="P5" s="3"/>
+      <c r="Q5" s="3"/>
+      <c r="R5" s="3"/>
     </row>
     <row r="6" spans="5:22">
       <c r="H6" s="2">
         <v>1</v>
       </c>
-      <c r="J6" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
-      <c r="M6" s="3"/>
-      <c r="O6" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="P6" s="3"/>
-      <c r="Q6" s="3"/>
-      <c r="R6" s="3"/>
+      <c r="J6" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="K6" s="7"/>
+      <c r="L6" s="7"/>
+      <c r="M6" s="7"/>
+      <c r="O6" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="P6" s="7"/>
+      <c r="Q6" s="7"/>
+      <c r="R6" s="7"/>
     </row>
     <row r="7" spans="5:22">
       <c r="H7" s="2">
         <v>2</v>
       </c>
-      <c r="J7" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-      <c r="M7" s="3"/>
-      <c r="O7" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="P7" s="3"/>
-      <c r="Q7" s="3"/>
-      <c r="R7" s="3"/>
+      <c r="J7" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="K7" s="7"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
+      <c r="O7" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="P7" s="7"/>
+      <c r="Q7" s="7"/>
+      <c r="R7" s="7"/>
     </row>
     <row r="8" spans="5:22">
       <c r="H8" s="2">
         <v>3</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3"/>
-      <c r="M8" s="3"/>
-      <c r="O8" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="P8" s="3"/>
-      <c r="Q8" s="3"/>
-      <c r="R8" s="3"/>
+      <c r="J8" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="K8" s="7"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="7"/>
+      <c r="O8" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="P8" s="7"/>
+      <c r="Q8" s="7"/>
+      <c r="R8" s="7"/>
     </row>
     <row r="9" spans="5:22">
       <c r="H9" s="2">
         <v>4</v>
       </c>
-      <c r="J9" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="K9" s="8"/>
-      <c r="L9" s="8"/>
-      <c r="M9" s="8"/>
-      <c r="O9" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="P9" s="8"/>
-      <c r="Q9" s="8"/>
-      <c r="R9" s="8"/>
+      <c r="J9" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="K9" s="7"/>
+      <c r="L9" s="7"/>
+      <c r="M9" s="7"/>
+      <c r="O9" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="P9" s="7"/>
+      <c r="Q9" s="7"/>
+      <c r="R9" s="7"/>
     </row>
     <row r="10" spans="5:22">
       <c r="H10" s="2">
         <v>5</v>
       </c>
-      <c r="J10" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="K10" s="8"/>
-      <c r="L10" s="8"/>
-      <c r="M10" s="8"/>
-      <c r="O10" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="P10" s="8"/>
-      <c r="Q10" s="8"/>
-      <c r="R10" s="8"/>
+      <c r="J10" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="K10" s="7"/>
+      <c r="L10" s="7"/>
+      <c r="M10" s="7"/>
+      <c r="O10" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="P10" s="7"/>
+      <c r="Q10" s="7"/>
+      <c r="R10" s="7"/>
     </row>
     <row r="11" spans="5:22">
       <c r="H11" s="2">
         <v>6</v>
       </c>
-      <c r="J11" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="K11" s="8"/>
-      <c r="L11" s="8"/>
-      <c r="M11" s="8"/>
-      <c r="O11" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="P11" s="8"/>
-      <c r="Q11" s="8"/>
-      <c r="R11" s="8"/>
+      <c r="J11" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="K11" s="7"/>
+      <c r="L11" s="7"/>
+      <c r="M11" s="7"/>
+      <c r="O11" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="P11" s="7"/>
+      <c r="Q11" s="7"/>
+      <c r="R11" s="7"/>
     </row>
     <row r="12" spans="5:22">
       <c r="H12" s="2">
         <v>7</v>
       </c>
-      <c r="J12" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K12" s="8"/>
-      <c r="L12" s="8"/>
-      <c r="M12" s="8"/>
-      <c r="O12" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="P12" s="8"/>
-      <c r="Q12" s="8"/>
-      <c r="R12" s="8"/>
+      <c r="J12" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="K12" s="7"/>
+      <c r="L12" s="7"/>
+      <c r="M12" s="7"/>
+      <c r="O12" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="P12" s="7"/>
+      <c r="Q12" s="7"/>
+      <c r="R12" s="7"/>
     </row>
     <row r="13" spans="5:22">
       <c r="H13" s="2">
         <v>8</v>
       </c>
-      <c r="J13" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="K13" s="8"/>
-      <c r="L13" s="8"/>
-      <c r="M13" s="8"/>
-      <c r="O13" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="P13" s="8"/>
-      <c r="Q13" s="8"/>
-      <c r="R13" s="8"/>
+      <c r="J13" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K13" s="7"/>
+      <c r="L13" s="7"/>
+      <c r="M13" s="7"/>
+      <c r="O13" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="P13" s="7"/>
+      <c r="Q13" s="7"/>
+      <c r="R13" s="7"/>
     </row>
     <row r="14" spans="5:22">
       <c r="H14" s="2">
         <v>9</v>
       </c>
-      <c r="J14" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="K14" s="8"/>
-      <c r="L14" s="8"/>
-      <c r="M14" s="8"/>
-      <c r="O14" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="P14" s="8"/>
-      <c r="Q14" s="8"/>
-      <c r="R14" s="8"/>
+      <c r="J14" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="K14" s="7"/>
+      <c r="L14" s="7"/>
+      <c r="M14" s="7"/>
+      <c r="O14" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="P14" s="7"/>
+      <c r="Q14" s="7"/>
+      <c r="R14" s="7"/>
     </row>
     <row r="15" spans="5:22">
       <c r="H15" s="2">
         <v>10</v>
       </c>
-      <c r="J15" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="K15" s="8"/>
-      <c r="L15" s="8"/>
-      <c r="M15" s="8"/>
-      <c r="O15" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P15" s="8"/>
-      <c r="Q15" s="8"/>
-      <c r="R15" s="8"/>
+      <c r="J15" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="K15" s="7"/>
+      <c r="L15" s="7"/>
+      <c r="M15" s="7"/>
+      <c r="O15" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="P15" s="7"/>
+      <c r="Q15" s="7"/>
+      <c r="R15" s="7"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="H6:H38">
     <sortCondition ref="H6"/>
   </sortState>
   <mergeCells count="25">
+    <mergeCell ref="O11:R11"/>
+    <mergeCell ref="O12:R12"/>
+    <mergeCell ref="O13:R13"/>
+    <mergeCell ref="O14:R14"/>
+    <mergeCell ref="O15:R15"/>
+    <mergeCell ref="O6:R6"/>
+    <mergeCell ref="O7:R7"/>
+    <mergeCell ref="O8:R8"/>
+    <mergeCell ref="O9:R9"/>
+    <mergeCell ref="O10:R10"/>
+    <mergeCell ref="J11:M11"/>
+    <mergeCell ref="J12:M12"/>
+    <mergeCell ref="J13:M13"/>
+    <mergeCell ref="J14:M14"/>
+    <mergeCell ref="J15:M15"/>
+    <mergeCell ref="J6:M6"/>
+    <mergeCell ref="J7:M7"/>
+    <mergeCell ref="J8:M8"/>
+    <mergeCell ref="J9:M9"/>
+    <mergeCell ref="J10:M10"/>
     <mergeCell ref="J5:M5"/>
     <mergeCell ref="O5:R5"/>
     <mergeCell ref="E1:V1"/>
     <mergeCell ref="E2:V2"/>
     <mergeCell ref="E3:V3"/>
-    <mergeCell ref="J6:M6"/>
-    <mergeCell ref="J7:M7"/>
-    <mergeCell ref="J8:M8"/>
-    <mergeCell ref="J9:M9"/>
-    <mergeCell ref="J10:M10"/>
-    <mergeCell ref="J11:M11"/>
-    <mergeCell ref="J12:M12"/>
-    <mergeCell ref="J13:M13"/>
-    <mergeCell ref="J14:M14"/>
-    <mergeCell ref="J15:M15"/>
-    <mergeCell ref="O6:R6"/>
-    <mergeCell ref="O7:R7"/>
-    <mergeCell ref="O8:R8"/>
-    <mergeCell ref="O9:R9"/>
-    <mergeCell ref="O10:R10"/>
-    <mergeCell ref="O11:R11"/>
-    <mergeCell ref="O12:R12"/>
-    <mergeCell ref="O13:R13"/>
-    <mergeCell ref="O14:R14"/>
-    <mergeCell ref="O15:R15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>

--- a/List_Books.xlsx
+++ b/List_Books.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68EB7091-8859-43F8-83CB-CF9955AC0EBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF19337E-1611-4E1E-B073-423727D8AE27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="29">
   <si>
     <t>Author</t>
   </si>
@@ -95,6 +95,18 @@
   </si>
   <si>
     <t>Book Name</t>
+  </si>
+  <si>
+    <t>Apple Stories</t>
+  </si>
+  <si>
+    <t>Samsung Stories</t>
+  </si>
+  <si>
+    <t>Steve Jobs</t>
+  </si>
+  <si>
+    <t>Hazard</t>
   </si>
 </sst>
 </file>
@@ -186,7 +198,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -194,6 +206,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -206,7 +219,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Good" xfId="1" builtinId="26"/>
@@ -491,7 +504,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="E1:V15"/>
+  <dimension ref="E1:V35"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="8.6640625" customWidth="1"/>
@@ -499,288 +512,452 @@
   </cols>
   <sheetData>
     <row r="1" spans="5:22" ht="15" customHeight="1">
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
-      <c r="N1" s="5"/>
-      <c r="O1" s="5"/>
-      <c r="P1" s="5"/>
-      <c r="Q1" s="5"/>
-      <c r="R1" s="5"/>
-      <c r="S1" s="5"/>
-      <c r="T1" s="5"/>
-      <c r="U1" s="5"/>
-      <c r="V1" s="5"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
+      <c r="O1" s="6"/>
+      <c r="P1" s="6"/>
+      <c r="Q1" s="6"/>
+      <c r="R1" s="6"/>
+      <c r="S1" s="6"/>
+      <c r="T1" s="6"/>
+      <c r="U1" s="6"/>
+      <c r="V1" s="6"/>
     </row>
     <row r="2" spans="5:22" ht="15" customHeight="1">
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6"/>
-      <c r="N2" s="6"/>
-      <c r="O2" s="6"/>
-      <c r="P2" s="6"/>
-      <c r="Q2" s="6"/>
-      <c r="R2" s="6"/>
-      <c r="S2" s="6"/>
-      <c r="T2" s="6"/>
-      <c r="U2" s="6"/>
-      <c r="V2" s="6"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="7"/>
+      <c r="M2" s="7"/>
+      <c r="N2" s="7"/>
+      <c r="O2" s="7"/>
+      <c r="P2" s="7"/>
+      <c r="Q2" s="7"/>
+      <c r="R2" s="7"/>
+      <c r="S2" s="7"/>
+      <c r="T2" s="7"/>
+      <c r="U2" s="7"/>
+      <c r="V2" s="7"/>
     </row>
     <row r="3" spans="5:22" ht="15" customHeight="1">
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="6"/>
-      <c r="K3" s="6"/>
-      <c r="L3" s="6"/>
-      <c r="M3" s="6"/>
-      <c r="N3" s="6"/>
-      <c r="O3" s="6"/>
-      <c r="P3" s="6"/>
-      <c r="Q3" s="6"/>
-      <c r="R3" s="6"/>
-      <c r="S3" s="6"/>
-      <c r="T3" s="6"/>
-      <c r="U3" s="6"/>
-      <c r="V3" s="6"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="7"/>
+      <c r="M3" s="7"/>
+      <c r="N3" s="7"/>
+      <c r="O3" s="7"/>
+      <c r="P3" s="7"/>
+      <c r="Q3" s="7"/>
+      <c r="R3" s="7"/>
+      <c r="S3" s="7"/>
+      <c r="T3" s="7"/>
+      <c r="U3" s="7"/>
+      <c r="V3" s="7"/>
     </row>
     <row r="5" spans="5:22">
       <c r="H5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="J5" s="3" t="s">
+      <c r="J5" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
-      <c r="M5" s="3"/>
-      <c r="O5" s="4" t="s">
+      <c r="K5" s="4"/>
+      <c r="L5" s="4"/>
+      <c r="M5" s="4"/>
+      <c r="O5" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="P5" s="3"/>
-      <c r="Q5" s="3"/>
-      <c r="R5" s="3"/>
+      <c r="P5" s="4"/>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="4"/>
     </row>
     <row r="6" spans="5:22">
       <c r="H6" s="2">
         <v>1</v>
       </c>
-      <c r="J6" s="7" t="s">
+      <c r="J6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K6" s="7"/>
-      <c r="L6" s="7"/>
-      <c r="M6" s="7"/>
-      <c r="O6" s="7" t="s">
+      <c r="K6" s="3"/>
+      <c r="L6" s="3"/>
+      <c r="M6" s="3"/>
+      <c r="O6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P6" s="7"/>
-      <c r="Q6" s="7"/>
-      <c r="R6" s="7"/>
+      <c r="P6" s="3"/>
+      <c r="Q6" s="3"/>
+      <c r="R6" s="3"/>
     </row>
     <row r="7" spans="5:22">
       <c r="H7" s="2">
         <v>2</v>
       </c>
-      <c r="J7" s="7" t="s">
+      <c r="J7" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="K7" s="7"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="7"/>
-      <c r="O7" s="7" t="s">
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3"/>
+      <c r="O7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="P7" s="7"/>
-      <c r="Q7" s="7"/>
-      <c r="R7" s="7"/>
+      <c r="P7" s="3"/>
+      <c r="Q7" s="3"/>
+      <c r="R7" s="3"/>
     </row>
     <row r="8" spans="5:22">
       <c r="H8" s="2">
         <v>3</v>
       </c>
-      <c r="J8" s="7" t="s">
+      <c r="J8" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="K8" s="7"/>
-      <c r="L8" s="7"/>
-      <c r="M8" s="7"/>
-      <c r="O8" s="7" t="s">
+      <c r="K8" s="3"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="3"/>
+      <c r="O8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P8" s="7"/>
-      <c r="Q8" s="7"/>
-      <c r="R8" s="7"/>
+      <c r="P8" s="3"/>
+      <c r="Q8" s="3"/>
+      <c r="R8" s="3"/>
     </row>
     <row r="9" spans="5:22">
       <c r="H9" s="2">
         <v>4</v>
       </c>
-      <c r="J9" s="7" t="s">
+      <c r="J9" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="K9" s="7"/>
-      <c r="L9" s="7"/>
-      <c r="M9" s="7"/>
-      <c r="O9" s="7" t="s">
+      <c r="K9" s="3"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="3"/>
+      <c r="O9" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P9" s="7"/>
-      <c r="Q9" s="7"/>
-      <c r="R9" s="7"/>
+      <c r="P9" s="3"/>
+      <c r="Q9" s="3"/>
+      <c r="R9" s="3"/>
     </row>
     <row r="10" spans="5:22">
       <c r="H10" s="2">
         <v>5</v>
       </c>
-      <c r="J10" s="7" t="s">
+      <c r="J10" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="K10" s="7"/>
-      <c r="L10" s="7"/>
-      <c r="M10" s="7"/>
-      <c r="O10" s="7" t="s">
+      <c r="K10" s="3"/>
+      <c r="L10" s="3"/>
+      <c r="M10" s="3"/>
+      <c r="O10" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="P10" s="7"/>
-      <c r="Q10" s="7"/>
-      <c r="R10" s="7"/>
+      <c r="P10" s="3"/>
+      <c r="Q10" s="3"/>
+      <c r="R10" s="3"/>
     </row>
     <row r="11" spans="5:22">
       <c r="H11" s="2">
         <v>6</v>
       </c>
-      <c r="J11" s="7" t="s">
+      <c r="J11" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="K11" s="7"/>
-      <c r="L11" s="7"/>
-      <c r="M11" s="7"/>
-      <c r="O11" s="7" t="s">
+      <c r="K11" s="3"/>
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+      <c r="O11" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="P11" s="7"/>
-      <c r="Q11" s="7"/>
-      <c r="R11" s="7"/>
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3"/>
+      <c r="R11" s="3"/>
     </row>
     <row r="12" spans="5:22">
       <c r="H12" s="2">
         <v>7</v>
       </c>
-      <c r="J12" s="7" t="s">
+      <c r="J12" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="K12" s="7"/>
-      <c r="L12" s="7"/>
-      <c r="M12" s="7"/>
-      <c r="O12" s="7" t="s">
+      <c r="K12" s="3"/>
+      <c r="L12" s="3"/>
+      <c r="M12" s="3"/>
+      <c r="O12" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="P12" s="7"/>
-      <c r="Q12" s="7"/>
-      <c r="R12" s="7"/>
+      <c r="P12" s="3"/>
+      <c r="Q12" s="3"/>
+      <c r="R12" s="3"/>
     </row>
     <row r="13" spans="5:22">
       <c r="H13" s="2">
         <v>8</v>
       </c>
-      <c r="J13" s="7" t="s">
+      <c r="J13" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="K13" s="7"/>
-      <c r="L13" s="7"/>
-      <c r="M13" s="7"/>
-      <c r="O13" s="7" t="s">
+      <c r="K13" s="3"/>
+      <c r="L13" s="3"/>
+      <c r="M13" s="3"/>
+      <c r="O13" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="P13" s="7"/>
-      <c r="Q13" s="7"/>
-      <c r="R13" s="7"/>
+      <c r="P13" s="3"/>
+      <c r="Q13" s="3"/>
+      <c r="R13" s="3"/>
     </row>
     <row r="14" spans="5:22">
       <c r="H14" s="2">
         <v>9</v>
       </c>
-      <c r="J14" s="7" t="s">
+      <c r="J14" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="K14" s="7"/>
-      <c r="L14" s="7"/>
-      <c r="M14" s="7"/>
-      <c r="O14" s="7" t="s">
+      <c r="K14" s="3"/>
+      <c r="L14" s="3"/>
+      <c r="M14" s="3"/>
+      <c r="O14" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="P14" s="7"/>
-      <c r="Q14" s="7"/>
-      <c r="R14" s="7"/>
+      <c r="P14" s="3"/>
+      <c r="Q14" s="3"/>
+      <c r="R14" s="3"/>
     </row>
     <row r="15" spans="5:22">
       <c r="H15" s="2">
         <v>10</v>
       </c>
-      <c r="J15" s="7" t="s">
+      <c r="J15" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K15" s="7"/>
-      <c r="L15" s="7"/>
-      <c r="M15" s="7"/>
-      <c r="O15" s="7" t="s">
+      <c r="K15" s="3"/>
+      <c r="L15" s="3"/>
+      <c r="M15" s="3"/>
+      <c r="O15" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="P15" s="7"/>
-      <c r="Q15" s="7"/>
-      <c r="R15" s="7"/>
+      <c r="P15" s="3"/>
+      <c r="Q15" s="3"/>
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="5:22">
+      <c r="H16" s="2">
+        <v>11</v>
+      </c>
+      <c r="J16" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="K16" s="8"/>
+      <c r="L16" s="8"/>
+      <c r="M16" s="8"/>
+      <c r="O16" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="P16" s="8"/>
+      <c r="Q16" s="8"/>
+      <c r="R16" s="8"/>
+    </row>
+    <row r="17" spans="8:18">
+      <c r="H17" s="2">
+        <v>12</v>
+      </c>
+      <c r="J17" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="K17" s="8"/>
+      <c r="L17" s="8"/>
+      <c r="M17" s="8"/>
+      <c r="O17" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="P17" s="8"/>
+      <c r="Q17" s="8"/>
+      <c r="R17" s="8"/>
+    </row>
+    <row r="18" spans="8:18">
+      <c r="J18" s="3"/>
+      <c r="K18" s="3"/>
+      <c r="L18" s="3"/>
+      <c r="M18" s="3"/>
+    </row>
+    <row r="19" spans="8:18">
+      <c r="J19" s="3"/>
+      <c r="K19" s="3"/>
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="8:18">
+      <c r="J20" s="3"/>
+      <c r="K20" s="3"/>
+      <c r="L20" s="3"/>
+      <c r="M20" s="3"/>
+    </row>
+    <row r="21" spans="8:18">
+      <c r="J21" s="3"/>
+      <c r="K21" s="3"/>
+      <c r="L21" s="3"/>
+      <c r="M21" s="3"/>
+    </row>
+    <row r="22" spans="8:18">
+      <c r="J22" s="3"/>
+      <c r="K22" s="3"/>
+      <c r="L22" s="3"/>
+      <c r="M22" s="3"/>
+    </row>
+    <row r="23" spans="8:18">
+      <c r="J23" s="3"/>
+      <c r="K23" s="3"/>
+      <c r="L23" s="3"/>
+      <c r="M23" s="3"/>
+    </row>
+    <row r="24" spans="8:18">
+      <c r="J24" s="3"/>
+      <c r="K24" s="3"/>
+      <c r="L24" s="3"/>
+      <c r="M24" s="3"/>
+    </row>
+    <row r="25" spans="8:18">
+      <c r="J25" s="3"/>
+      <c r="K25" s="3"/>
+      <c r="L25" s="3"/>
+      <c r="M25" s="3"/>
+    </row>
+    <row r="26" spans="8:18">
+      <c r="J26" s="3"/>
+      <c r="K26" s="3"/>
+      <c r="L26" s="3"/>
+      <c r="M26" s="3"/>
+    </row>
+    <row r="27" spans="8:18">
+      <c r="J27" s="3"/>
+      <c r="K27" s="3"/>
+      <c r="L27" s="3"/>
+      <c r="M27" s="3"/>
+    </row>
+    <row r="28" spans="8:18">
+      <c r="J28" s="3"/>
+      <c r="K28" s="3"/>
+      <c r="L28" s="3"/>
+      <c r="M28" s="3"/>
+    </row>
+    <row r="29" spans="8:18">
+      <c r="J29" s="3"/>
+      <c r="K29" s="3"/>
+      <c r="L29" s="3"/>
+      <c r="M29" s="3"/>
+    </row>
+    <row r="30" spans="8:18">
+      <c r="J30" s="3"/>
+      <c r="K30" s="3"/>
+      <c r="L30" s="3"/>
+      <c r="M30" s="3"/>
+    </row>
+    <row r="31" spans="8:18">
+      <c r="J31" s="3"/>
+      <c r="K31" s="3"/>
+      <c r="L31" s="3"/>
+      <c r="M31" s="3"/>
+    </row>
+    <row r="32" spans="8:18">
+      <c r="J32" s="3"/>
+      <c r="K32" s="3"/>
+      <c r="L32" s="3"/>
+      <c r="M32" s="3"/>
+    </row>
+    <row r="33" spans="10:13">
+      <c r="J33" s="3"/>
+      <c r="K33" s="3"/>
+      <c r="L33" s="3"/>
+      <c r="M33" s="3"/>
+    </row>
+    <row r="34" spans="10:13">
+      <c r="J34" s="3"/>
+      <c r="K34" s="3"/>
+      <c r="L34" s="3"/>
+      <c r="M34" s="3"/>
+    </row>
+    <row r="35" spans="10:13">
+      <c r="J35" s="3"/>
+      <c r="K35" s="3"/>
+      <c r="L35" s="3"/>
+      <c r="M35" s="3"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="H6:H38">
     <sortCondition ref="H6"/>
   </sortState>
-  <mergeCells count="25">
+  <mergeCells count="47">
+    <mergeCell ref="O16:R16"/>
+    <mergeCell ref="O17:R17"/>
+    <mergeCell ref="J31:M31"/>
+    <mergeCell ref="J32:M32"/>
+    <mergeCell ref="J33:M33"/>
+    <mergeCell ref="J34:M34"/>
+    <mergeCell ref="J35:M35"/>
+    <mergeCell ref="J26:M26"/>
+    <mergeCell ref="J27:M27"/>
+    <mergeCell ref="J28:M28"/>
+    <mergeCell ref="J29:M29"/>
+    <mergeCell ref="J30:M30"/>
+    <mergeCell ref="J21:M21"/>
+    <mergeCell ref="J22:M22"/>
+    <mergeCell ref="J23:M23"/>
+    <mergeCell ref="J24:M24"/>
+    <mergeCell ref="J25:M25"/>
+    <mergeCell ref="J16:M16"/>
+    <mergeCell ref="J17:M17"/>
+    <mergeCell ref="J18:M18"/>
+    <mergeCell ref="J19:M19"/>
+    <mergeCell ref="J20:M20"/>
+    <mergeCell ref="J5:M5"/>
+    <mergeCell ref="O5:R5"/>
+    <mergeCell ref="E1:V1"/>
+    <mergeCell ref="E2:V2"/>
+    <mergeCell ref="E3:V3"/>
+    <mergeCell ref="J6:M6"/>
+    <mergeCell ref="J7:M7"/>
+    <mergeCell ref="J8:M8"/>
+    <mergeCell ref="J9:M9"/>
+    <mergeCell ref="J10:M10"/>
+    <mergeCell ref="J11:M11"/>
+    <mergeCell ref="J12:M12"/>
+    <mergeCell ref="J13:M13"/>
+    <mergeCell ref="J14:M14"/>
+    <mergeCell ref="J15:M15"/>
+    <mergeCell ref="O6:R6"/>
+    <mergeCell ref="O7:R7"/>
+    <mergeCell ref="O8:R8"/>
+    <mergeCell ref="O9:R9"/>
+    <mergeCell ref="O10:R10"/>
     <mergeCell ref="O11:R11"/>
     <mergeCell ref="O12:R12"/>
     <mergeCell ref="O13:R13"/>
     <mergeCell ref="O14:R14"/>
     <mergeCell ref="O15:R15"/>
-    <mergeCell ref="O6:R6"/>
-    <mergeCell ref="O7:R7"/>
-    <mergeCell ref="O8:R8"/>
-    <mergeCell ref="O9:R9"/>
-    <mergeCell ref="O10:R10"/>
-    <mergeCell ref="J11:M11"/>
-    <mergeCell ref="J12:M12"/>
-    <mergeCell ref="J13:M13"/>
-    <mergeCell ref="J14:M14"/>
-    <mergeCell ref="J15:M15"/>
-    <mergeCell ref="J6:M6"/>
-    <mergeCell ref="J7:M7"/>
-    <mergeCell ref="J8:M8"/>
-    <mergeCell ref="J9:M9"/>
-    <mergeCell ref="J10:M10"/>
-    <mergeCell ref="J5:M5"/>
-    <mergeCell ref="O5:R5"/>
-    <mergeCell ref="E1:V1"/>
-    <mergeCell ref="E2:V2"/>
-    <mergeCell ref="E3:V3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>

--- a/List_Books.xlsx
+++ b/List_Books.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF19337E-1611-4E1E-B073-423727D8AE27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7404307-5D2B-463A-9E71-F962097C71EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="31">
   <si>
     <t>Author</t>
   </si>
@@ -107,6 +107,12 @@
   </si>
   <si>
     <t>Hazard</t>
+  </si>
+  <si>
+    <t>HP</t>
+  </si>
+  <si>
+    <t>GH</t>
   </si>
 </sst>
 </file>
@@ -768,41 +774,52 @@
       <c r="H16" s="2">
         <v>11</v>
       </c>
-      <c r="J16" s="8" t="s">
+      <c r="J16" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="K16" s="8"/>
-      <c r="L16" s="8"/>
-      <c r="M16" s="8"/>
-      <c r="O16" s="8" t="s">
+      <c r="K16" s="3"/>
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+      <c r="O16" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="P16" s="8"/>
-      <c r="Q16" s="8"/>
-      <c r="R16" s="8"/>
+      <c r="P16" s="3"/>
+      <c r="Q16" s="3"/>
+      <c r="R16" s="3"/>
     </row>
     <row r="17" spans="8:18">
       <c r="H17" s="2">
         <v>12</v>
       </c>
-      <c r="J17" s="8" t="s">
+      <c r="J17" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="K17" s="8"/>
-      <c r="L17" s="8"/>
-      <c r="M17" s="8"/>
-      <c r="O17" s="8" t="s">
+      <c r="K17" s="3"/>
+      <c r="L17" s="3"/>
+      <c r="M17" s="3"/>
+      <c r="O17" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="P17" s="8"/>
-      <c r="Q17" s="8"/>
-      <c r="R17" s="8"/>
+      <c r="P17" s="3"/>
+      <c r="Q17" s="3"/>
+      <c r="R17" s="3"/>
     </row>
     <row r="18" spans="8:18">
-      <c r="J18" s="3"/>
-      <c r="K18" s="3"/>
-      <c r="L18" s="3"/>
-      <c r="M18" s="3"/>
+      <c r="H18" s="2">
+        <v>13</v>
+      </c>
+      <c r="J18" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="K18" s="8"/>
+      <c r="L18" s="8"/>
+      <c r="M18" s="8"/>
+      <c r="O18" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="P18" s="8"/>
+      <c r="Q18" s="8"/>
+      <c r="R18" s="8"/>
     </row>
     <row r="19" spans="8:18">
       <c r="J19" s="3"/>
@@ -910,12 +927,32 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="H6:H38">
     <sortCondition ref="H6"/>
   </sortState>
-  <mergeCells count="47">
-    <mergeCell ref="O16:R16"/>
-    <mergeCell ref="O17:R17"/>
-    <mergeCell ref="J31:M31"/>
-    <mergeCell ref="J32:M32"/>
-    <mergeCell ref="J33:M33"/>
+  <mergeCells count="48">
+    <mergeCell ref="O11:R11"/>
+    <mergeCell ref="O12:R12"/>
+    <mergeCell ref="O13:R13"/>
+    <mergeCell ref="O14:R14"/>
+    <mergeCell ref="O15:R15"/>
+    <mergeCell ref="O6:R6"/>
+    <mergeCell ref="O7:R7"/>
+    <mergeCell ref="O8:R8"/>
+    <mergeCell ref="O9:R9"/>
+    <mergeCell ref="O10:R10"/>
+    <mergeCell ref="J11:M11"/>
+    <mergeCell ref="J12:M12"/>
+    <mergeCell ref="J13:M13"/>
+    <mergeCell ref="J14:M14"/>
+    <mergeCell ref="J15:M15"/>
+    <mergeCell ref="J6:M6"/>
+    <mergeCell ref="J7:M7"/>
+    <mergeCell ref="J8:M8"/>
+    <mergeCell ref="J9:M9"/>
+    <mergeCell ref="J10:M10"/>
+    <mergeCell ref="J5:M5"/>
+    <mergeCell ref="O5:R5"/>
+    <mergeCell ref="E1:V1"/>
+    <mergeCell ref="E2:V2"/>
+    <mergeCell ref="E3:V3"/>
     <mergeCell ref="J34:M34"/>
     <mergeCell ref="J35:M35"/>
     <mergeCell ref="J26:M26"/>
@@ -923,6 +960,11 @@
     <mergeCell ref="J28:M28"/>
     <mergeCell ref="J29:M29"/>
     <mergeCell ref="J30:M30"/>
+    <mergeCell ref="O16:R16"/>
+    <mergeCell ref="O17:R17"/>
+    <mergeCell ref="J31:M31"/>
+    <mergeCell ref="J32:M32"/>
+    <mergeCell ref="J33:M33"/>
     <mergeCell ref="J21:M21"/>
     <mergeCell ref="J22:M22"/>
     <mergeCell ref="J23:M23"/>
@@ -933,31 +975,7 @@
     <mergeCell ref="J18:M18"/>
     <mergeCell ref="J19:M19"/>
     <mergeCell ref="J20:M20"/>
-    <mergeCell ref="J5:M5"/>
-    <mergeCell ref="O5:R5"/>
-    <mergeCell ref="E1:V1"/>
-    <mergeCell ref="E2:V2"/>
-    <mergeCell ref="E3:V3"/>
-    <mergeCell ref="J6:M6"/>
-    <mergeCell ref="J7:M7"/>
-    <mergeCell ref="J8:M8"/>
-    <mergeCell ref="J9:M9"/>
-    <mergeCell ref="J10:M10"/>
-    <mergeCell ref="J11:M11"/>
-    <mergeCell ref="J12:M12"/>
-    <mergeCell ref="J13:M13"/>
-    <mergeCell ref="J14:M14"/>
-    <mergeCell ref="J15:M15"/>
-    <mergeCell ref="O6:R6"/>
-    <mergeCell ref="O7:R7"/>
-    <mergeCell ref="O8:R8"/>
-    <mergeCell ref="O9:R9"/>
-    <mergeCell ref="O10:R10"/>
-    <mergeCell ref="O11:R11"/>
-    <mergeCell ref="O12:R12"/>
-    <mergeCell ref="O13:R13"/>
-    <mergeCell ref="O14:R14"/>
-    <mergeCell ref="O15:R15"/>
+    <mergeCell ref="O18:R18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>

--- a/List_Books.xlsx
+++ b/List_Books.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7404307-5D2B-463A-9E71-F962097C71EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A5E98A0-6D71-4A22-9F2D-FBD66BC03415}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,9 +31,6 @@
     <t>ADD THE BOOKS NAME AND THE AUTHOR USING THIS TEMPLATE</t>
   </si>
   <si>
-    <t>DO NOT CHANGE ANYTHING, CLICK SAVE AND IMPORT THIS FILES TO GUI</t>
-  </si>
-  <si>
     <t>BIL</t>
   </si>
   <si>
@@ -113,6 +110,9 @@
   </si>
   <si>
     <t>GH</t>
+  </si>
+  <si>
+    <t>DO NOT CHANGE ANYTHING, CLICK SAVE AND IMPORT THIS FILES TO LMS APPLICATION</t>
   </si>
 </sst>
 </file>
@@ -204,7 +204,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -225,7 +225,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Good" xfId="1" builtinId="26"/>
@@ -563,7 +562,7 @@
     </row>
     <row r="3" spans="5:22" ht="15" customHeight="1">
       <c r="E3" s="7" t="s">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="F3" s="7"/>
       <c r="G3" s="7"/>
@@ -585,10 +584,10 @@
     </row>
     <row r="5" spans="5:22">
       <c r="H5" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -605,13 +604,13 @@
         <v>1</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
       <c r="O6" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P6" s="3"/>
       <c r="Q6" s="3"/>
@@ -622,13 +621,13 @@
         <v>2</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
       <c r="O7" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P7" s="3"/>
       <c r="Q7" s="3"/>
@@ -639,13 +638,13 @@
         <v>3</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
       <c r="O8" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P8" s="3"/>
       <c r="Q8" s="3"/>
@@ -656,13 +655,13 @@
         <v>4</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
       <c r="O9" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P9" s="3"/>
       <c r="Q9" s="3"/>
@@ -673,13 +672,13 @@
         <v>5</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
       <c r="O10" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P10" s="3"/>
       <c r="Q10" s="3"/>
@@ -690,13 +689,13 @@
         <v>6</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="O11" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
@@ -707,13 +706,13 @@
         <v>7</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
       <c r="O12" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="P12" s="3"/>
       <c r="Q12" s="3"/>
@@ -724,13 +723,13 @@
         <v>8</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
       <c r="M13" s="3"/>
       <c r="O13" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="P13" s="3"/>
       <c r="Q13" s="3"/>
@@ -741,13 +740,13 @@
         <v>9</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
       <c r="M14" s="3"/>
       <c r="O14" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P14" s="3"/>
       <c r="Q14" s="3"/>
@@ -758,13 +757,13 @@
         <v>10</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
       <c r="O15" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P15" s="3"/>
       <c r="Q15" s="3"/>
@@ -775,13 +774,13 @@
         <v>11</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="O16" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
@@ -792,13 +791,13 @@
         <v>12</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>
       <c r="M17" s="3"/>
       <c r="O17" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P17" s="3"/>
       <c r="Q17" s="3"/>
@@ -808,18 +807,18 @@
       <c r="H18" s="2">
         <v>13</v>
       </c>
-      <c r="J18" s="8" t="s">
+      <c r="J18" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K18" s="3"/>
+      <c r="L18" s="3"/>
+      <c r="M18" s="3"/>
+      <c r="O18" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="K18" s="8"/>
-      <c r="L18" s="8"/>
-      <c r="M18" s="8"/>
-      <c r="O18" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="P18" s="8"/>
-      <c r="Q18" s="8"/>
-      <c r="R18" s="8"/>
+      <c r="P18" s="3"/>
+      <c r="Q18" s="3"/>
+      <c r="R18" s="3"/>
     </row>
     <row r="19" spans="8:18">
       <c r="J19" s="3"/>
@@ -928,38 +927,6 @@
     <sortCondition ref="H6"/>
   </sortState>
   <mergeCells count="48">
-    <mergeCell ref="O11:R11"/>
-    <mergeCell ref="O12:R12"/>
-    <mergeCell ref="O13:R13"/>
-    <mergeCell ref="O14:R14"/>
-    <mergeCell ref="O15:R15"/>
-    <mergeCell ref="O6:R6"/>
-    <mergeCell ref="O7:R7"/>
-    <mergeCell ref="O8:R8"/>
-    <mergeCell ref="O9:R9"/>
-    <mergeCell ref="O10:R10"/>
-    <mergeCell ref="J11:M11"/>
-    <mergeCell ref="J12:M12"/>
-    <mergeCell ref="J13:M13"/>
-    <mergeCell ref="J14:M14"/>
-    <mergeCell ref="J15:M15"/>
-    <mergeCell ref="J6:M6"/>
-    <mergeCell ref="J7:M7"/>
-    <mergeCell ref="J8:M8"/>
-    <mergeCell ref="J9:M9"/>
-    <mergeCell ref="J10:M10"/>
-    <mergeCell ref="J5:M5"/>
-    <mergeCell ref="O5:R5"/>
-    <mergeCell ref="E1:V1"/>
-    <mergeCell ref="E2:V2"/>
-    <mergeCell ref="E3:V3"/>
-    <mergeCell ref="J34:M34"/>
-    <mergeCell ref="J35:M35"/>
-    <mergeCell ref="J26:M26"/>
-    <mergeCell ref="J27:M27"/>
-    <mergeCell ref="J28:M28"/>
-    <mergeCell ref="J29:M29"/>
-    <mergeCell ref="J30:M30"/>
     <mergeCell ref="O16:R16"/>
     <mergeCell ref="O17:R17"/>
     <mergeCell ref="J31:M31"/>
@@ -976,6 +943,38 @@
     <mergeCell ref="J19:M19"/>
     <mergeCell ref="J20:M20"/>
     <mergeCell ref="O18:R18"/>
+    <mergeCell ref="J34:M34"/>
+    <mergeCell ref="J35:M35"/>
+    <mergeCell ref="J26:M26"/>
+    <mergeCell ref="J27:M27"/>
+    <mergeCell ref="J28:M28"/>
+    <mergeCell ref="J29:M29"/>
+    <mergeCell ref="J30:M30"/>
+    <mergeCell ref="J5:M5"/>
+    <mergeCell ref="O5:R5"/>
+    <mergeCell ref="E1:V1"/>
+    <mergeCell ref="E2:V2"/>
+    <mergeCell ref="E3:V3"/>
+    <mergeCell ref="J6:M6"/>
+    <mergeCell ref="J7:M7"/>
+    <mergeCell ref="J8:M8"/>
+    <mergeCell ref="J9:M9"/>
+    <mergeCell ref="J10:M10"/>
+    <mergeCell ref="J11:M11"/>
+    <mergeCell ref="J12:M12"/>
+    <mergeCell ref="J13:M13"/>
+    <mergeCell ref="J14:M14"/>
+    <mergeCell ref="J15:M15"/>
+    <mergeCell ref="O6:R6"/>
+    <mergeCell ref="O7:R7"/>
+    <mergeCell ref="O8:R8"/>
+    <mergeCell ref="O9:R9"/>
+    <mergeCell ref="O10:R10"/>
+    <mergeCell ref="O11:R11"/>
+    <mergeCell ref="O12:R12"/>
+    <mergeCell ref="O13:R13"/>
+    <mergeCell ref="O14:R14"/>
+    <mergeCell ref="O15:R15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
